--- a/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
+++ b/РАБОЧИЙ СТОЛ/СЫРЫ перемещение/Перемещение.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\СЫРЫ перемещение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684E1586-DE62-4F17-830F-38173F0C4A91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8027DF0-84F7-4F2D-84C0-90AFD5CBB584}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t>Продукт белково-жировой Сметанковый 50% ВЕС Коровино Останкино</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>да</t>
+  </si>
+  <si>
+    <t>НЕТ</t>
+  </si>
+  <si>
+    <t>кг (инвенторизация)</t>
   </si>
 </sst>
 </file>
@@ -509,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95.5703125" customWidth="1"/>
@@ -522,12 +528,12 @@
     <col min="8" max="8" width="18" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -550,7 +556,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,7 +578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -598,8 +604,17 @@
       <c r="I4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4">
+        <v>-61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -625,8 +640,11 @@
       <c r="I5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -650,13 +668,16 @@
       <c r="I6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -677,7 +698,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -704,7 +725,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -730,8 +751,11 @@
       <c r="I11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -757,8 +781,11 @@
       <c r="I12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -787,7 +814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -804,7 +831,7 @@
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
